--- a/output/Results_combined_BT_GPGLMM.xlsx
+++ b/output/Results_combined_BT_GPGLMM.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Definitive_Paper_Taxonomy</t>
+          <t>Paper_Taxonomy</t>
         </is>
       </c>
     </row>
